--- a/data/trans_orig/IP31KM16_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM16_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1483</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7071</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3913</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33912</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30364</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35952</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>45200</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41848</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>41207</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37619</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41372</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37569</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>43696</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>156</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>86571</t>
+          <t>75119</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81720</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89375</t>
+          <t>77805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21598</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14789</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29363</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24506</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17364</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34449</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>42972</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62336</t>
+          <t>53124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>135444</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>127679</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>142253</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>134793</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>124850</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>141935</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>124144</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149089</t>
+          <t>116150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164650</t>
+          <t>130182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>292090</t>
+          <t>259588</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278923</t>
+          <t>249436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>301270</t>
+          <t>268279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29052</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21461</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30916</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32886</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53723</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>179014</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>169812</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185787</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>152326</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144020</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158406</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,01%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>191029</t>
+          <t>152989</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181574</t>
+          <t>143275</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>198459</t>
+          <t>159290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>343356</t>
+          <t>332003</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331840</t>
+          <t>319844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352677</t>
+          <t>341562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41355</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28812</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68463</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>39670</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26951</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57235</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43725</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76930</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>83395</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63183</t>
+          <t>61344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117682</t>
+          <t>105147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>250866</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>223758</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>263409</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>234597</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>217032</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>247316</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>261274</t>
+          <t>219247</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228069</t>
+          <t>208467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274667</t>
+          <t>227856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>495871</t>
+          <t>470113</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>461584</t>
+          <t>442411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>516083</t>
+          <t>486214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87588</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70780</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>112471</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>86218</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69400</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107035</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76109</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130845</t>
+          <t>96009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168208</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154711</t>
+          <t>145236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215729</t>
+          <t>195757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>599236</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>574353</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>616044</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>566916</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>546099</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>583734</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>650972</t>
+          <t>537587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>613888</t>
+          <t>522199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>668624</t>
+          <t>550680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1217888</t>
+          <t>1136823</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1182138</t>
+          <t>1109274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1243156</t>
+          <t>1159795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
